--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$159</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5561" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="660">
   <si>
     <t>Property</t>
   </si>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -671,7 +671,7 @@
     <t>durchfuehrungsabsicht</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2026.0.1}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2027.0.0-ballot.rc1}
 </t>
   </si>
   <si>
@@ -699,7 +699,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.extension:durchfuehrungsabsicht.value[x].id</t>
@@ -1067,7 +1067,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.category.coding:sct.id</t>
@@ -1314,6 +1314,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -1823,6 +1826,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2381,7 +2400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM158"/>
+  <dimension ref="A1:AM159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -2394,7 +2413,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.31640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="115.3046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4625,7 +4644,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>113</v>
@@ -4845,7 +4864,7 @@
         <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
@@ -10060,7 +10079,7 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>113</v>
@@ -10391,7 +10410,7 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>113</v>
@@ -10609,7 +10628,7 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>97</v>
@@ -10829,7 +10848,7 @@
         <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>113</v>
@@ -10942,7 +10961,7 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>97</v>
@@ -11053,7 +11072,7 @@
         <v>85</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
@@ -11104,7 +11123,9 @@
       <c r="M79" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O79" t="s" s="2">
         <v>244</v>
       </c>
@@ -11164,7 +11185,7 @@
         <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>97</v>
@@ -11181,10 +11202,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11215,7 +11236,9 @@
       <c r="M80" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O80" t="s" s="2">
         <v>251</v>
       </c>
@@ -11275,7 +11298,7 @@
         <v>85</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>97</v>
@@ -11292,10 +11315,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11388,7 +11411,7 @@
         <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>97</v>
@@ -11405,7 +11428,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>376</v>
@@ -11434,7 +11457,7 @@
         <v>126</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>227</v>
@@ -11450,7 +11473,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>76</v>
@@ -11501,7 +11524,7 @@
         <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>97</v>
@@ -11518,7 +11541,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>377</v>
@@ -11547,10 +11570,10 @@
         <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>237</v>
@@ -11612,7 +11635,7 @@
         <v>85</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>97</v>
@@ -11629,7 +11652,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>378</v>
@@ -11658,12 +11681,14 @@
         <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O84" t="s" s="2">
         <v>244</v>
       </c>
@@ -11678,7 +11703,7 @@
         <v>76</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>76</v>
@@ -11723,10 +11748,10 @@
         <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>76</v>
@@ -11740,7 +11765,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>379</v>
@@ -11774,7 +11799,9 @@
       <c r="M85" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N85" s="2"/>
+      <c r="N85" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O85" t="s" s="2">
         <v>251</v>
       </c>
@@ -11834,7 +11861,7 @@
         <v>85</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>97</v>
@@ -11851,7 +11878,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>380</v>
@@ -11947,7 +11974,7 @@
         <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>97</v>
@@ -11964,7 +11991,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>372</v>
@@ -12033,7 +12060,7 @@
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>76</v>
@@ -12077,7 +12104,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>374</v>
@@ -12186,7 +12213,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>375</v>
@@ -12297,7 +12324,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>376</v>
@@ -12410,7 +12437,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>377</v>
@@ -12521,7 +12548,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>378</v>
@@ -12632,7 +12659,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>379</v>
@@ -12743,7 +12770,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>380</v>
@@ -12856,10 +12883,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12969,14 +12996,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12995,13 +13022,13 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13052,7 +13079,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>85</v>
@@ -13067,21 +13094,21 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13187,10 +13214,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13298,10 +13325,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13327,13 +13354,13 @@
         <v>99</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13383,7 +13410,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13392,7 +13419,7 @@
         <v>85</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>97</v>
@@ -13409,10 +13436,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13438,13 +13465,13 @@
         <v>126</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13473,10 +13500,10 @@
         <v>142</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>76</v>
@@ -13494,7 +13521,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13520,10 +13547,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13549,13 +13576,13 @@
         <v>269</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13605,7 +13632,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13631,10 +13658,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13660,13 +13687,13 @@
         <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13716,7 +13743,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13742,10 +13769,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13768,16 +13795,16 @@
         <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13827,7 +13854,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13842,21 +13869,21 @@
         <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13962,10 +13989,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14073,10 +14100,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14102,13 +14129,13 @@
         <v>99</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14158,7 +14185,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14167,7 +14194,7 @@
         <v>85</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>97</v>
@@ -14184,10 +14211,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14213,13 +14240,13 @@
         <v>126</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14248,10 +14275,10 @@
         <v>142</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>76</v>
@@ -14269,7 +14296,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14295,10 +14322,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14324,13 +14351,13 @@
         <v>269</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14380,7 +14407,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14406,10 +14433,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14435,13 +14462,13 @@
         <v>99</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14491,7 +14518,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14517,10 +14544,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14543,16 +14570,16 @@
         <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14590,7 +14617,7 @@
         <v>76</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
@@ -14600,7 +14627,7 @@
         <v>373</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14615,24 +14642,24 @@
         <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>76</v>
@@ -14657,13 +14684,13 @@
         <v>204</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14713,7 +14740,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14728,24 +14755,24 @@
         <v>97</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>76</v>
@@ -14767,16 +14794,16 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14826,7 +14853,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14841,21 +14868,21 @@
         <v>97</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14878,13 +14905,13 @@
         <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14935,7 +14962,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -14953,7 +14980,7 @@
         <v>76</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>76</v>
@@ -14961,10 +14988,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14987,13 +15014,13 @@
         <v>86</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15044,7 +15071,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15062,7 +15089,7 @@
         <v>76</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>76</v>
@@ -15070,10 +15097,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15096,13 +15123,13 @@
         <v>86</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15153,7 +15180,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15168,7 +15195,7 @@
         <v>97</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>76</v>
@@ -15179,10 +15206,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15288,10 +15315,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15399,14 +15426,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15428,10 +15455,10 @@
         <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>108</v>
@@ -15486,7 +15513,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15512,10 +15539,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15541,14 +15568,14 @@
         <v>309</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -15576,10 +15603,10 @@
         <v>150</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>76</v>
@@ -15597,7 +15624,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15612,21 +15639,21 @@
         <v>97</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15649,17 +15676,17 @@
         <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>76</v>
@@ -15708,7 +15735,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>85</v>
@@ -15723,21 +15750,21 @@
         <v>97</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15760,17 +15787,17 @@
         <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>76</v>
@@ -15819,7 +15846,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15845,10 +15872,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15871,17 +15898,17 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -15930,7 +15957,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -15948,7 +15975,7 @@
         <v>76</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>76</v>
@@ -15956,10 +15983,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15985,13 +16012,13 @@
         <v>309</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16020,10 +16047,10 @@
         <v>150</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>76</v>
@@ -16041,7 +16068,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -16056,10 +16083,10 @@
         <v>97</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>76</v>
@@ -16067,10 +16094,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16093,16 +16120,16 @@
         <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16152,7 +16179,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -16167,10 +16194,10 @@
         <v>97</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>76</v>
@@ -16178,10 +16205,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16207,13 +16234,13 @@
         <v>309</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16243,7 +16270,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>76</v>
@@ -16261,7 +16288,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16282,15 +16309,15 @@
         <v>76</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16396,10 +16423,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16507,46 +16534,44 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="C128" s="2"/>
+      <c r="C128" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>138</v>
+        <v>579</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>325</v>
+        <v>580</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>76</v>
       </c>
@@ -16582,17 +16607,19 @@
         <v>76</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AC128" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -16604,7 +16631,7 @@
         <v>76</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>76</v>
@@ -16613,15 +16640,15 @@
         <v>76</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16629,31 +16656,35 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
       </c>
@@ -16689,31 +16720,29 @@
         <v>76</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>76</v>
@@ -16722,26 +16751,26 @@
         <v>76</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>76</v>
+        <v>331</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>76</v>
@@ -16753,17 +16782,15 @@
         <v>76</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>76</v>
@@ -16800,31 +16827,31 @@
         <v>76</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>76</v>
@@ -16838,21 +16865,21 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>76</v>
@@ -16861,23 +16888,21 @@
         <v>76</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>76</v>
       </c>
@@ -16913,31 +16938,31 @@
         <v>76</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>76</v>
@@ -16946,15 +16971,15 @@
         <v>76</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>232</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16962,13 +16987,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>76</v>
@@ -16977,18 +17002,20 @@
         <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
       </c>
@@ -17036,7 +17063,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -17057,15 +17084,15 @@
         <v>76</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17073,13 +17100,13 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>76</v>
@@ -17088,18 +17115,18 @@
         <v>86</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>76</v>
       </c>
@@ -17147,7 +17174,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -17168,15 +17195,15 @@
         <v>76</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17199,17 +17226,17 @@
         <v>86</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
@@ -17258,7 +17285,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -17279,15 +17306,15 @@
         <v>76</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17310,19 +17337,17 @@
         <v>86</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -17371,7 +17396,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -17392,31 +17417,29 @@
         <v>76</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>76</v>
@@ -17425,19 +17448,19 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>334</v>
+        <v>257</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>335</v>
+        <v>258</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>327</v>
+        <v>259</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
@@ -17486,13 +17509,13 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>330</v>
+        <v>261</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>76</v>
@@ -17507,47 +17530,53 @@
         <v>76</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>331</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>100</v>
+        <v>334</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>76</v>
       </c>
@@ -17595,19 +17624,19 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>76</v>
@@ -17616,26 +17645,26 @@
         <v>76</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>76</v>
+        <v>331</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>76</v>
@@ -17647,17 +17676,15 @@
         <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>76</v>
@@ -17694,31 +17721,31 @@
         <v>76</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>76</v>
@@ -17730,48 +17757,46 @@
         <v>76</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>76</v>
       </c>
@@ -17780,7 +17805,7 @@
         <v>76</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>76</v>
@@ -17807,31 +17832,31 @@
         <v>76</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>76</v>
@@ -17840,15 +17865,15 @@
         <v>76</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>232</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17871,18 +17896,20 @@
         <v>86</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>76</v>
       </c>
@@ -17891,7 +17918,7 @@
         <v>76</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>76</v>
@@ -17930,7 +17957,7 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
@@ -17951,15 +17978,15 @@
         <v>76</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17982,18 +18009,18 @@
         <v>86</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>76</v>
       </c>
@@ -18041,7 +18068,7 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -18062,15 +18089,15 @@
         <v>76</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18078,13 +18105,13 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>76</v>
@@ -18093,17 +18120,17 @@
         <v>86</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>76</v>
@@ -18152,7 +18179,7 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>77</v>
@@ -18173,15 +18200,15 @@
         <v>76</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18204,19 +18231,17 @@
         <v>86</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>76</v>
@@ -18265,7 +18290,7 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>77</v>
@@ -18286,15 +18311,15 @@
         <v>76</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18317,19 +18342,19 @@
         <v>86</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>99</v>
+        <v>256</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>76</v>
@@ -18378,7 +18403,7 @@
         <v>76</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>357</v>
+        <v>261</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
@@ -18399,15 +18424,15 @@
         <v>76</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>358</v>
+        <v>262</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18430,18 +18455,20 @@
         <v>86</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>596</v>
+        <v>353</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>597</v>
+        <v>354</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
       </c>
@@ -18465,13 +18492,13 @@
         <v>76</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>599</v>
+        <v>76</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>600</v>
+        <v>76</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>76</v>
@@ -18489,7 +18516,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>595</v>
+        <v>357</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>77</v>
@@ -18510,7 +18537,7 @@
         <v>76</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>76</v>
+        <v>358</v>
       </c>
     </row>
     <row r="146" hidden="true">
@@ -18529,7 +18556,7 @@
         <v>77</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>76</v>
@@ -18538,19 +18565,19 @@
         <v>76</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -18576,13 +18603,13 @@
         <v>76</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>76</v>
+        <v>605</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>76</v>
+        <v>606</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -18606,7 +18633,7 @@
         <v>77</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>76</v>
@@ -18626,10 +18653,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18652,16 +18679,16 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>309</v>
+        <v>608</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18687,13 +18714,13 @@
         <v>76</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>610</v>
+        <v>76</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>611</v>
+        <v>76</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>76</v>
@@ -18711,7 +18738,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -18763,18 +18790,18 @@
         <v>76</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N148" s="2"/>
-      <c r="O148" t="s" s="2">
-        <v>616</v>
-      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>76</v>
       </c>
@@ -18798,13 +18825,13 @@
         <v>76</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>76</v>
+        <v>616</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>76</v>
+        <v>617</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>76</v>
@@ -18848,10 +18875,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18874,16 +18901,18 @@
         <v>76</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>309</v>
+        <v>619</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+      <c r="O149" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
       </c>
@@ -18907,13 +18936,13 @@
         <v>76</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>620</v>
+        <v>76</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>621</v>
+        <v>76</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>76</v>
@@ -18931,7 +18960,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -18955,12 +18984,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18974,7 +19003,7 @@
         <v>78</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>76</v>
@@ -18983,7 +19012,7 @@
         <v>76</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>623</v>
+        <v>309</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>624</v>
@@ -19016,13 +19045,13 @@
         <v>76</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>76</v>
+        <v>626</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>76</v>
+        <v>627</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>76</v>
@@ -19040,7 +19069,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
@@ -19055,13 +19084,13 @@
         <v>97</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>626</v>
+        <v>76</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>627</v>
+        <v>76</v>
       </c>
     </row>
     <row r="151">
@@ -19077,7 +19106,7 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>78</v>
@@ -19092,13 +19121,13 @@
         <v>76</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>516</v>
+        <v>629</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19164,21 +19193,21 @@
         <v>97</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>76</v>
+        <v>632</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>76</v>
+        <v>633</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19186,13 +19215,13 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>76</v>
@@ -19201,13 +19230,13 @@
         <v>76</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>99</v>
+        <v>517</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>100</v>
+        <v>635</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>101</v>
+        <v>636</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19258,19 +19287,19 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>102</v>
+        <v>634</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>76</v>
@@ -19284,21 +19313,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>76</v>
@@ -19310,17 +19339,15 @@
         <v>76</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>76</v>
@@ -19369,19 +19396,19 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>76</v>
@@ -19395,14 +19422,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>523</v>
+        <v>104</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -19415,26 +19442,24 @@
         <v>76</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>525</v>
+        <v>107</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="O154" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>76</v>
       </c>
@@ -19482,7 +19507,7 @@
         <v>76</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>526</v>
+        <v>112</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>77</v>
@@ -19508,42 +19533,46 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>309</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>635</v>
+        <v>525</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>76</v>
       </c>
@@ -19567,13 +19596,13 @@
         <v>76</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>637</v>
+        <v>76</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>638</v>
+        <v>76</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>76</v>
@@ -19591,19 +19620,19 @@
         <v>76</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>634</v>
+        <v>527</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>76</v>
@@ -19615,12 +19644,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19628,13 +19657,13 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>76</v>
@@ -19643,7 +19672,7 @@
         <v>76</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>640</v>
+        <v>309</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>641</v>
@@ -19676,13 +19705,13 @@
         <v>76</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>76</v>
+        <v>643</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>76</v>
+        <v>644</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>76</v>
@@ -19700,10 +19729,10 @@
         <v>76</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>85</v>
@@ -19724,12 +19753,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19737,13 +19766,13 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>76</v>
@@ -19752,20 +19781,16 @@
         <v>76</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O157" t="s" s="2">
         <v>648</v>
       </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>76</v>
       </c>
@@ -19813,13 +19838,13 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>76</v>
@@ -19865,18 +19890,20 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>309</v>
+        <v>650</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>76</v>
       </c>
@@ -19900,13 +19927,13 @@
         <v>76</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>652</v>
+        <v>76</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>653</v>
+        <v>76</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>76</v>
@@ -19948,8 +19975,119 @@
         <v>76</v>
       </c>
     </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM158">
+  <autoFilter ref="A1:AM159">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19959,7 +20097,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI157">
+  <conditionalFormatting sqref="A2:AI158">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -1816,7 +1816,10 @@
 </t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-koerperstelle-snomedct|2027.0.0-ballot.rc1</t>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>OBX-20</t>
@@ -1876,6 +1879,9 @@
   </si>
   <si>
     <t>snomed-ct</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-koerperstelle-snomedct|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding:snomed-ct.id</t>
@@ -16266,11 +16272,13 @@
         <v>76</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>76</v>
@@ -16309,15 +16317,15 @@
         <v>76</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16423,10 +16431,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16534,13 +16542,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="B128" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="C128" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>76</v>
@@ -16562,13 +16570,13 @@
         <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -16645,10 +16653,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16720,7 +16728,7 @@
         <v>76</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
@@ -16756,10 +16764,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16865,10 +16873,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16976,10 +16984,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17089,10 +17097,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17200,10 +17208,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17311,10 +17319,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17422,10 +17430,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17535,13 +17543,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>76</v>
@@ -17600,13 +17608,11 @@
         <v>76</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>76</v>
@@ -17650,10 +17656,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17759,10 +17765,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17870,10 +17876,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17983,10 +17989,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18094,10 +18100,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18205,10 +18211,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18316,10 +18322,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18429,10 +18435,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18542,10 +18548,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18571,13 +18577,13 @@
         <v>309</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -18606,10 +18612,10 @@
         <v>150</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -18627,7 +18633,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -18653,10 +18659,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18679,16 +18685,16 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18738,7 +18744,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -18764,10 +18770,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18793,13 +18799,13 @@
         <v>309</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -18828,10 +18834,10 @@
         <v>150</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>76</v>
@@ -18849,7 +18855,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -18875,10 +18881,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18901,17 +18907,17 @@
         <v>76</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -18960,7 +18966,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -18986,10 +18992,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19015,10 +19021,10 @@
         <v>309</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -19048,10 +19054,10 @@
         <v>150</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>76</v>
@@ -19069,7 +19075,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
@@ -19095,10 +19101,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19121,13 +19127,13 @@
         <v>76</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19178,7 +19184,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -19193,21 +19199,21 @@
         <v>97</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19233,10 +19239,10 @@
         <v>517</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19287,7 +19293,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -19313,10 +19319,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19422,10 +19428,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19533,10 +19539,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19646,10 +19652,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19675,10 +19681,10 @@
         <v>309</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -19708,10 +19714,10 @@
         <v>164</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>76</v>
@@ -19729,7 +19735,7 @@
         <v>76</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
@@ -19755,10 +19761,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19781,13 +19787,13 @@
         <v>76</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -19838,7 +19844,7 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>85</v>
@@ -19864,10 +19870,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19890,19 +19896,19 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>76</v>
@@ -19951,7 +19957,7 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>77</v>
@@ -19977,10 +19983,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20006,13 +20012,13 @@
         <v>309</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -20041,10 +20047,10 @@
         <v>150</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>76</v>
@@ -20062,7 +20068,7 @@
         <v>76</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>77</v>
